--- a/test files/Biblio- Grand 25.Invo.xlsx
+++ b/test files/Biblio- Grand 25.Invo.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27932"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\batcave\work\Credit_App\Credit_app_v3_test\test files\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32B0042B-FC7E-4E43-8EDC-B73FE3A4F5E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="75" windowWidth="15480" windowHeight="10920"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="statment" sheetId="22" r:id="rId1"/>
@@ -22,7 +28,20 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">statment!$A$1:$I$12</definedName>
   </definedNames>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -113,12 +132,12 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="_-* #,##0.00_-;_-* #,##0.00\-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="165" formatCode="dd/mm/yyyy;@"/>
   </numFmts>
-  <fonts count="16">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -675,66 +694,74 @@
   <cellStyles count="59">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 10 2" xfId="2"/>
-    <cellStyle name="Normal 10 3" xfId="3"/>
-    <cellStyle name="Normal 10 4" xfId="4"/>
-    <cellStyle name="Normal 101" xfId="45"/>
-    <cellStyle name="Normal 104" xfId="46"/>
-    <cellStyle name="Normal 107" xfId="48"/>
-    <cellStyle name="Normal 110" xfId="49"/>
-    <cellStyle name="Normal 116" xfId="50"/>
-    <cellStyle name="Normal 119" xfId="51"/>
-    <cellStyle name="Normal 123" xfId="53"/>
-    <cellStyle name="Normal 127" xfId="54"/>
-    <cellStyle name="Normal 130" xfId="55"/>
-    <cellStyle name="Normal 133" xfId="56"/>
-    <cellStyle name="Normal 136" xfId="57"/>
-    <cellStyle name="Normal 140" xfId="5"/>
-    <cellStyle name="Normal 148" xfId="6"/>
-    <cellStyle name="Normal 149" xfId="7"/>
-    <cellStyle name="Normal 151" xfId="8"/>
-    <cellStyle name="Normal 152" xfId="40"/>
-    <cellStyle name="Normal 153" xfId="9"/>
-    <cellStyle name="Normal 154" xfId="10"/>
-    <cellStyle name="Normal 157" xfId="38"/>
-    <cellStyle name="Normal 158" xfId="39"/>
-    <cellStyle name="Normal 159" xfId="11"/>
-    <cellStyle name="Normal 160" xfId="12"/>
-    <cellStyle name="Normal 162" xfId="13"/>
-    <cellStyle name="Normal 163" xfId="14"/>
-    <cellStyle name="Normal 165" xfId="15"/>
-    <cellStyle name="Normal 166" xfId="16"/>
-    <cellStyle name="Normal 19 2" xfId="17"/>
-    <cellStyle name="Normal 19 3" xfId="18"/>
-    <cellStyle name="Normal 19 4" xfId="19"/>
-    <cellStyle name="Normal 2" xfId="47"/>
-    <cellStyle name="Normal 2 2" xfId="20"/>
-    <cellStyle name="Normal 2 3" xfId="21"/>
-    <cellStyle name="Normal 2 4" xfId="22"/>
-    <cellStyle name="Normal 20 2" xfId="23"/>
-    <cellStyle name="Normal 20 3" xfId="24"/>
-    <cellStyle name="Normal 20 4" xfId="25"/>
-    <cellStyle name="Normal 23 2" xfId="26"/>
-    <cellStyle name="Normal 23 3" xfId="27"/>
-    <cellStyle name="Normal 23 4" xfId="28"/>
-    <cellStyle name="Normal 3" xfId="41"/>
-    <cellStyle name="Normal 37 2" xfId="29"/>
-    <cellStyle name="Normal 37 3" xfId="30"/>
-    <cellStyle name="Normal 37 4" xfId="31"/>
-    <cellStyle name="Normal 38 2" xfId="32"/>
-    <cellStyle name="Normal 38 3" xfId="33"/>
-    <cellStyle name="Normal 38 4" xfId="34"/>
-    <cellStyle name="Normal 5" xfId="42"/>
-    <cellStyle name="Normal 9 2" xfId="35"/>
-    <cellStyle name="Normal 9 3" xfId="36"/>
-    <cellStyle name="Normal 9 4" xfId="37"/>
-    <cellStyle name="Normal 94" xfId="43"/>
-    <cellStyle name="Normal 98" xfId="44"/>
-    <cellStyle name="Normal_Biblio Globus" xfId="52"/>
-    <cellStyle name="Normal_Biblio Globus_1" xfId="58"/>
+    <cellStyle name="Normal 10 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
+    <cellStyle name="Normal 10 3" xfId="3" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
+    <cellStyle name="Normal 10 4" xfId="4" xr:uid="{00000000-0005-0000-0000-000004000000}"/>
+    <cellStyle name="Normal 101" xfId="45" xr:uid="{00000000-0005-0000-0000-000005000000}"/>
+    <cellStyle name="Normal 104" xfId="46" xr:uid="{00000000-0005-0000-0000-000006000000}"/>
+    <cellStyle name="Normal 107" xfId="48" xr:uid="{00000000-0005-0000-0000-000007000000}"/>
+    <cellStyle name="Normal 110" xfId="49" xr:uid="{00000000-0005-0000-0000-000008000000}"/>
+    <cellStyle name="Normal 116" xfId="50" xr:uid="{00000000-0005-0000-0000-000009000000}"/>
+    <cellStyle name="Normal 119" xfId="51" xr:uid="{00000000-0005-0000-0000-00000A000000}"/>
+    <cellStyle name="Normal 123" xfId="53" xr:uid="{00000000-0005-0000-0000-00000B000000}"/>
+    <cellStyle name="Normal 127" xfId="54" xr:uid="{00000000-0005-0000-0000-00000C000000}"/>
+    <cellStyle name="Normal 130" xfId="55" xr:uid="{00000000-0005-0000-0000-00000D000000}"/>
+    <cellStyle name="Normal 133" xfId="56" xr:uid="{00000000-0005-0000-0000-00000E000000}"/>
+    <cellStyle name="Normal 136" xfId="57" xr:uid="{00000000-0005-0000-0000-00000F000000}"/>
+    <cellStyle name="Normal 140" xfId="5" xr:uid="{00000000-0005-0000-0000-000010000000}"/>
+    <cellStyle name="Normal 148" xfId="6" xr:uid="{00000000-0005-0000-0000-000011000000}"/>
+    <cellStyle name="Normal 149" xfId="7" xr:uid="{00000000-0005-0000-0000-000012000000}"/>
+    <cellStyle name="Normal 151" xfId="8" xr:uid="{00000000-0005-0000-0000-000013000000}"/>
+    <cellStyle name="Normal 152" xfId="40" xr:uid="{00000000-0005-0000-0000-000014000000}"/>
+    <cellStyle name="Normal 153" xfId="9" xr:uid="{00000000-0005-0000-0000-000015000000}"/>
+    <cellStyle name="Normal 154" xfId="10" xr:uid="{00000000-0005-0000-0000-000016000000}"/>
+    <cellStyle name="Normal 157" xfId="38" xr:uid="{00000000-0005-0000-0000-000017000000}"/>
+    <cellStyle name="Normal 158" xfId="39" xr:uid="{00000000-0005-0000-0000-000018000000}"/>
+    <cellStyle name="Normal 159" xfId="11" xr:uid="{00000000-0005-0000-0000-000019000000}"/>
+    <cellStyle name="Normal 160" xfId="12" xr:uid="{00000000-0005-0000-0000-00001A000000}"/>
+    <cellStyle name="Normal 162" xfId="13" xr:uid="{00000000-0005-0000-0000-00001B000000}"/>
+    <cellStyle name="Normal 163" xfId="14" xr:uid="{00000000-0005-0000-0000-00001C000000}"/>
+    <cellStyle name="Normal 165" xfId="15" xr:uid="{00000000-0005-0000-0000-00001D000000}"/>
+    <cellStyle name="Normal 166" xfId="16" xr:uid="{00000000-0005-0000-0000-00001E000000}"/>
+    <cellStyle name="Normal 19 2" xfId="17" xr:uid="{00000000-0005-0000-0000-00001F000000}"/>
+    <cellStyle name="Normal 19 3" xfId="18" xr:uid="{00000000-0005-0000-0000-000020000000}"/>
+    <cellStyle name="Normal 19 4" xfId="19" xr:uid="{00000000-0005-0000-0000-000021000000}"/>
+    <cellStyle name="Normal 2" xfId="47" xr:uid="{00000000-0005-0000-0000-000022000000}"/>
+    <cellStyle name="Normal 2 2" xfId="20" xr:uid="{00000000-0005-0000-0000-000023000000}"/>
+    <cellStyle name="Normal 2 3" xfId="21" xr:uid="{00000000-0005-0000-0000-000024000000}"/>
+    <cellStyle name="Normal 2 4" xfId="22" xr:uid="{00000000-0005-0000-0000-000025000000}"/>
+    <cellStyle name="Normal 20 2" xfId="23" xr:uid="{00000000-0005-0000-0000-000026000000}"/>
+    <cellStyle name="Normal 20 3" xfId="24" xr:uid="{00000000-0005-0000-0000-000027000000}"/>
+    <cellStyle name="Normal 20 4" xfId="25" xr:uid="{00000000-0005-0000-0000-000028000000}"/>
+    <cellStyle name="Normal 23 2" xfId="26" xr:uid="{00000000-0005-0000-0000-000029000000}"/>
+    <cellStyle name="Normal 23 3" xfId="27" xr:uid="{00000000-0005-0000-0000-00002A000000}"/>
+    <cellStyle name="Normal 23 4" xfId="28" xr:uid="{00000000-0005-0000-0000-00002B000000}"/>
+    <cellStyle name="Normal 3" xfId="41" xr:uid="{00000000-0005-0000-0000-00002C000000}"/>
+    <cellStyle name="Normal 37 2" xfId="29" xr:uid="{00000000-0005-0000-0000-00002D000000}"/>
+    <cellStyle name="Normal 37 3" xfId="30" xr:uid="{00000000-0005-0000-0000-00002E000000}"/>
+    <cellStyle name="Normal 37 4" xfId="31" xr:uid="{00000000-0005-0000-0000-00002F000000}"/>
+    <cellStyle name="Normal 38 2" xfId="32" xr:uid="{00000000-0005-0000-0000-000030000000}"/>
+    <cellStyle name="Normal 38 3" xfId="33" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
+    <cellStyle name="Normal 38 4" xfId="34" xr:uid="{00000000-0005-0000-0000-000032000000}"/>
+    <cellStyle name="Normal 5" xfId="42" xr:uid="{00000000-0005-0000-0000-000033000000}"/>
+    <cellStyle name="Normal 9 2" xfId="35" xr:uid="{00000000-0005-0000-0000-000034000000}"/>
+    <cellStyle name="Normal 9 3" xfId="36" xr:uid="{00000000-0005-0000-0000-000035000000}"/>
+    <cellStyle name="Normal 9 4" xfId="37" xr:uid="{00000000-0005-0000-0000-000036000000}"/>
+    <cellStyle name="Normal 94" xfId="43" xr:uid="{00000000-0005-0000-0000-000037000000}"/>
+    <cellStyle name="Normal 98" xfId="44" xr:uid="{00000000-0005-0000-0000-000038000000}"/>
+    <cellStyle name="Normal_Biblio Globus" xfId="52" xr:uid="{00000000-0005-0000-0000-000039000000}"/>
+    <cellStyle name="Normal_Biblio Globus_1" xfId="58" xr:uid="{00000000-0005-0000-0000-00003A000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -755,7 +782,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="1025" name="Picture 1"/>
+        <xdr:cNvPr id="1025" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
         </xdr:cNvPicPr>
@@ -800,7 +833,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2049" name="Picture 1"/>
+        <xdr:cNvPr id="2049" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000001080000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
         </xdr:cNvPicPr>
@@ -840,7 +879,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Picture 2"/>
+        <xdr:cNvPr id="3" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000003000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -878,7 +923,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="Picture 4"/>
+        <xdr:cNvPr id="5" name="Picture 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000005000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -921,7 +972,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="Picture 3"/>
+        <xdr:cNvPr id="4" name="Picture 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000004000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -959,7 +1016,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="Picture 4"/>
+        <xdr:cNvPr id="5" name="Picture 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000005000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -1002,7 +1065,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Picture 2"/>
+        <xdr:cNvPr id="3" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000003000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -1040,7 +1109,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="Picture 3"/>
+        <xdr:cNvPr id="4" name="Picture 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000004000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -1078,7 +1153,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="Picture 4"/>
+        <xdr:cNvPr id="5" name="Picture 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000005000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -1121,7 +1202,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="Picture 3"/>
+        <xdr:cNvPr id="4" name="Picture 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0400-000004000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -1159,7 +1246,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Picture 2"/>
+        <xdr:cNvPr id="3" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0400-000003000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -1202,7 +1295,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Picture 2"/>
+        <xdr:cNvPr id="3" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0500-000003000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -1240,7 +1339,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="Picture 3"/>
+        <xdr:cNvPr id="4" name="Picture 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0500-000004000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -1278,7 +1383,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="6" name="Picture 5"/>
+        <xdr:cNvPr id="6" name="Picture 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0500-000006000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -1316,7 +1427,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="Picture 4"/>
+        <xdr:cNvPr id="5" name="Picture 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0500-000005000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -1343,7 +1460,24 @@
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <oleLink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" progId="Excel.Sheet.12">
+    <oleItems>
+      <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+        <mc:Choice Requires="x14">
+          <x14:oleItem name="!Sheet1!R17C8:R18C8" advise="1"/>
+        </mc:Choice>
+        <mc:Fallback>
+          <oleItem name="!Sheet1!R17C8:R18C8" advise="1"/>
+        </mc:Fallback>
+      </mc:AlternateContent>
+    </oleItems>
+  </oleLink>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="Feb 2024"/>
@@ -1363,8 +1497,8 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="nov.2023"/>
@@ -1390,20 +1524,10 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <oleLink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" progId="Excel.Sheet.12">
-    <oleItems>
-      <oleItem name="!Sheet1!R17C8:R18C8" advise="1"/>
-    </oleItems>
-  </oleLink>
-</externalLink>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1441,7 +1565,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -1475,6 +1599,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -1509,9 +1634,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1684,16 +1810,16 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I33"/>
-  <sheetFormatPr defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.42578125" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="9" width="20.7109375" style="2" customWidth="1"/>
-    <col min="10" max="16384" width="9.140625" style="2"/>
+    <col min="1" max="1" width="18.44140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="9" width="20.6640625" style="2" customWidth="1"/>
+    <col min="10" max="16384" width="9.109375" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="20.25" thickTop="1" thickBot="1">
+    <row r="1" spans="1:9" ht="18.600000000000001" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
         <v>8</v>
       </c>
@@ -1722,7 +1848,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:9" s="6" customFormat="1" ht="15" thickTop="1">
+    <row r="2" spans="1:9" s="6" customFormat="1" ht="14.4" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A2" s="23">
         <v>45779</v>
       </c>
@@ -1742,7 +1868,7 @@
         <v>16</v>
       </c>
       <c r="G2" s="29">
-        <f t="shared" ref="G2:G7" si="0">+E2-D2</f>
+        <f t="shared" ref="G2:G4" si="0">+E2-D2</f>
         <v>9</v>
       </c>
       <c r="H2" s="42">
@@ -1753,7 +1879,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="3" spans="1:9" s="25" customFormat="1" ht="14.25">
+    <row r="3" spans="1:9" s="25" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A3" s="23">
         <v>45799</v>
       </c>
@@ -1784,7 +1910,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="14.25">
+    <row r="4" spans="1:9" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A4" s="23">
         <v>45768</v>
       </c>
@@ -1815,16 +1941,16 @@
         <v>544</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="14.25">
+    <row r="5" spans="1:9" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A5" s="23">
         <v>45757</v>
       </c>
       <c r="B5" s="22">
         <v>116305309455</v>
       </c>
-      <c r="C5" s="40">
-        <f t="array" ref="C5:C6">[3]!'!Sheet1!R17C8:R18C8'</f>
-        <v>152482</v>
+      <c r="C5" s="40" t="e">
+        <f t="array" ref="C5:C6">[1]!'!Sheet1!R17C8:R18C8'</f>
+        <v>#REF!</v>
       </c>
       <c r="D5" s="1">
         <v>45804</v>
@@ -1847,15 +1973,15 @@
         <v>368</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="14.25">
+    <row r="6" spans="1:9" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A6" s="23">
         <v>45757</v>
       </c>
       <c r="B6" s="22">
         <v>116305309905</v>
       </c>
-      <c r="C6" s="41">
-        <v>152483</v>
+      <c r="C6" s="41" t="e">
+        <v>#REF!</v>
       </c>
       <c r="D6" s="1">
         <v>45804</v>
@@ -1878,7 +2004,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="14.25">
+    <row r="7" spans="1:9" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A7" s="23">
         <v>45757</v>
       </c>
@@ -1909,7 +2035,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="14.25">
+    <row r="8" spans="1:9" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A8" s="23">
         <v>45762</v>
       </c>
@@ -1940,7 +2066,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="14.25">
+    <row r="9" spans="1:9" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A9" s="23">
         <v>45808</v>
       </c>
@@ -1971,7 +2097,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="14.25">
+    <row r="10" spans="1:9" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A10" s="23">
         <v>45806</v>
       </c>
@@ -2002,7 +2128,7 @@
         <v>714</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="14.25">
+    <row r="11" spans="1:9" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A11" s="23">
         <v>45806</v>
       </c>
@@ -2033,7 +2159,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="14.25">
+    <row r="12" spans="1:9" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A12" s="23">
         <v>45805</v>
       </c>
@@ -2064,7 +2190,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="14.25">
+    <row r="13" spans="1:9" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A13" s="23">
         <v>45806</v>
       </c>
@@ -2095,7 +2221,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="14.25">
+    <row r="14" spans="1:9" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A14" s="23">
         <v>45783</v>
       </c>
@@ -2126,7 +2252,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="14.25">
+    <row r="15" spans="1:9" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A15" s="23">
         <v>45808</v>
       </c>
@@ -2157,7 +2283,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="14.25">
+    <row r="16" spans="1:9" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A16" s="23">
         <v>45781</v>
       </c>
@@ -2188,7 +2314,7 @@
         <v>1116</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="14.25">
+    <row r="17" spans="1:9" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A17" s="23">
         <v>45781</v>
       </c>
@@ -2219,7 +2345,7 @@
         <v>1116</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="14.25">
+    <row r="18" spans="1:9" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A18" s="23">
         <v>45815</v>
       </c>
@@ -2250,7 +2376,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="19" spans="1:9" ht="14.25">
+    <row r="19" spans="1:9" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A19" s="23">
         <v>45793</v>
       </c>
@@ -2281,7 +2407,7 @@
         <v>658</v>
       </c>
     </row>
-    <row r="20" spans="1:9" ht="14.25">
+    <row r="20" spans="1:9" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A20" s="23">
         <v>45819</v>
       </c>
@@ -2312,7 +2438,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="21" spans="1:9" ht="14.25">
+    <row r="21" spans="1:9" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A21" s="23">
         <v>45781</v>
       </c>
@@ -2343,7 +2469,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="22" spans="1:9" ht="14.25">
+    <row r="22" spans="1:9" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A22" s="23">
         <v>45822</v>
       </c>
@@ -2374,38 +2500,48 @@
         <v>294</v>
       </c>
     </row>
-    <row r="33" spans="8:8">
+    <row r="33" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H33" s="2">
         <f>558*2</f>
         <v>1116</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I12"/>
-  <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F11">
-      <formula1>'[1]rate code'!$A$1:$A$15</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F12">
-      <formula1>'[2]rate code'!$A$1:$A$15</formula1>
-    </dataValidation>
-  </dataValidations>
+  <autoFilter ref="A1:I12" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000000000000}">
+          <x14:formula1>
+            <xm:f>'C:\Users\Area-Credit2\AppData\Local\Microsoft\Windows\INetCache\Content.Outlook\R4F19B9Y\[biblio Globus.xls]rate code'!#REF!</xm:f>
+          </x14:formula1>
+          <xm:sqref>F2:F11</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000001000000}">
+          <x14:formula1>
+            <xm:f>'C:\Users\Area-Credit2\AppData\Local\Microsoft\Windows\INetCache\Content.Outlook\R4F19B9Y\[biblio  Globus (3).xls]rate code'!#REF!</xm:f>
+          </x14:formula1>
+          <xm:sqref>F12</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:N27"/>
-  <sheetFormatPr defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="11" width="15.7109375" style="2" customWidth="1"/>
-    <col min="12" max="16384" width="9.140625" style="2"/>
+    <col min="1" max="11" width="15.6640625" style="2" customWidth="1"/>
+    <col min="12" max="16384" width="9.109375" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="16.5" thickTop="1">
+    <row r="1" spans="1:14" ht="16.2" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A1" s="9" t="s">
         <v>5</v>
       </c>
@@ -2449,7 +2585,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:14" ht="14.25">
+    <row r="2" spans="1:14" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A2" s="13">
         <v>45200</v>
       </c>
@@ -2493,7 +2629,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="3" spans="1:14" ht="14.25">
+    <row r="3" spans="1:14" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A3" s="17">
         <v>45231</v>
       </c>
@@ -2537,7 +2673,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="4" spans="1:14" ht="14.25">
+    <row r="4" spans="1:14" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A4" s="17">
         <v>45246</v>
       </c>
@@ -2581,7 +2717,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="5" spans="1:14" ht="14.25">
+    <row r="5" spans="1:14" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A5" s="17">
         <v>45289</v>
       </c>
@@ -2625,7 +2761,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="6" spans="1:14" ht="14.25">
+    <row r="6" spans="1:14" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A6" s="17">
         <v>45302</v>
       </c>
@@ -2669,7 +2805,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="7" spans="1:14" ht="15" thickBot="1">
+    <row r="7" spans="1:14" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="18">
         <v>45338</v>
       </c>
@@ -2713,7 +2849,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="8" spans="1:14" ht="15" thickTop="1">
+    <row r="8" spans="1:14" ht="14.4" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A8" s="17">
         <v>45413</v>
       </c>
@@ -2766,7 +2902,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="9" spans="1:14" ht="14.25">
+    <row r="9" spans="1:14" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A9" s="17">
         <v>45428</v>
       </c>
@@ -2819,7 +2955,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="10" spans="1:14" ht="14.25">
+    <row r="10" spans="1:14" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A10" s="17">
         <v>45444</v>
       </c>
@@ -2872,7 +3008,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="11" spans="1:14" ht="14.25">
+    <row r="11" spans="1:14" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A11" s="17">
         <v>45474</v>
       </c>
@@ -2925,7 +3061,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="12" spans="1:14" ht="14.25">
+    <row r="12" spans="1:14" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A12" s="17">
         <v>45505</v>
       </c>
@@ -2978,7 +3114,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="13" spans="1:14" ht="14.25">
+    <row r="13" spans="1:14" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A13" s="27">
         <v>45536</v>
       </c>
@@ -3031,7 +3167,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="14" spans="1:14" ht="15" thickBot="1">
+    <row r="14" spans="1:14" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="18">
         <v>45566</v>
       </c>
@@ -3084,7 +3220,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="15" spans="1:14" ht="15" thickTop="1">
+    <row r="15" spans="1:14" ht="14.4" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A15" s="17">
         <v>45597</v>
       </c>
@@ -3137,7 +3273,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="16" spans="1:14" ht="14.25">
+    <row r="16" spans="1:14" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A16" s="17">
         <v>45612</v>
       </c>
@@ -3190,7 +3326,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="17" spans="1:14" ht="14.25">
+    <row r="17" spans="1:14" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A17" s="17">
         <v>45655</v>
       </c>
@@ -3243,7 +3379,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="18" spans="1:14" ht="14.25">
+    <row r="18" spans="1:14" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A18" s="17">
         <v>45668</v>
       </c>
@@ -3296,7 +3432,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="19" spans="1:14" ht="14.25">
+    <row r="19" spans="1:14" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A19" s="27">
         <v>45704</v>
       </c>
@@ -3349,7 +3485,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="20" spans="1:14" ht="15" thickBot="1">
+    <row r="20" spans="1:14" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="18">
         <v>45778</v>
       </c>
@@ -3402,7 +3538,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="21" spans="1:14" ht="15" thickTop="1">
+    <row r="21" spans="1:14" ht="14.4" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A21" s="17">
         <v>45793</v>
       </c>
@@ -3455,7 +3591,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="22" spans="1:14" ht="14.25">
+    <row r="22" spans="1:14" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A22" s="17">
         <v>45809</v>
       </c>
@@ -3508,7 +3644,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="23" spans="1:14" ht="14.25">
+    <row r="23" spans="1:14" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A23" s="17">
         <v>45839</v>
       </c>
@@ -3561,7 +3697,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="24" spans="1:14" ht="14.25">
+    <row r="24" spans="1:14" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A24" s="17">
         <v>45870</v>
       </c>
@@ -3614,7 +3750,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="25" spans="1:14" ht="14.25">
+    <row r="25" spans="1:14" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A25" s="27">
         <v>45901</v>
       </c>
@@ -3667,7 +3803,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="26" spans="1:14" ht="15" thickBot="1">
+    <row r="26" spans="1:14" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="18">
         <v>45931</v>
       </c>
@@ -3720,36 +3856,46 @@
         <v>177</v>
       </c>
     </row>
-    <row r="27" spans="1:14" ht="13.5" thickTop="1">
+    <row r="27" spans="1:14" ht="13.8" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A27" s="26"/>
     </row>
   </sheetData>
-  <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J1 L1:M1 C1:D1 G1:H1">
-      <formula1>'[1]rate code'!$A$1:$A$15</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I1">
-      <formula1>'[2]rate code'!$A$1:$A$15</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-000000000000}">
+          <x14:formula1>
+            <xm:f>'C:\Users\Area-Credit2\AppData\Local\Microsoft\Windows\INetCache\Content.Outlook\R4F19B9Y\[biblio Globus.xls]rate code'!#REF!</xm:f>
+          </x14:formula1>
+          <xm:sqref>J1 L1:M1 C1:D1 G1:H1</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-000001000000}">
+          <x14:formula1>
+            <xm:f>'C:\Users\Area-Credit2\AppData\Local\Microsoft\Windows\INetCache\Content.Outlook\R4F19B9Y\[biblio  Globus (3).xls]rate code'!#REF!</xm:f>
+          </x14:formula1>
+          <xm:sqref>I1</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:N5"/>
-  <sheetFormatPr defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.28515625" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.5703125" style="2" customWidth="1"/>
-    <col min="3" max="13" width="12.7109375" style="2" customWidth="1"/>
-    <col min="14" max="16384" width="9.140625" style="2"/>
+    <col min="1" max="1" width="11.33203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.5546875" style="2" customWidth="1"/>
+    <col min="3" max="13" width="12.6640625" style="2" customWidth="1"/>
+    <col min="14" max="16384" width="9.109375" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="16.5" thickTop="1">
+    <row r="1" spans="1:14" ht="16.2" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A1" s="30" t="s">
         <v>5</v>
       </c>
@@ -3793,7 +3939,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:14" ht="14.25">
+    <row r="2" spans="1:14" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A2" s="32">
         <v>45668</v>
       </c>
@@ -3846,7 +3992,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="3" spans="1:14" ht="14.25">
+    <row r="3" spans="1:14" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A3" s="32">
         <v>45717</v>
       </c>
@@ -3899,7 +4045,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="4" spans="1:14" ht="14.25">
+    <row r="4" spans="1:14" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A4" s="32">
         <v>45764</v>
       </c>
@@ -3952,7 +4098,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="5" spans="1:14" ht="14.25">
+    <row r="5" spans="1:14" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A5" s="32">
         <v>45788</v>
       </c>
@@ -4006,32 +4152,42 @@
       </c>
     </row>
   </sheetData>
-  <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J1 L1:M1 C1:D1 G1:H1">
-      <formula1>'[1]rate code'!$A$1:$A$15</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I1">
-      <formula1>'[2]rate code'!$A$1:$A$15</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0200-000000000000}">
+          <x14:formula1>
+            <xm:f>'C:\Users\Area-Credit2\AppData\Local\Microsoft\Windows\INetCache\Content.Outlook\R4F19B9Y\[biblio Globus.xls]rate code'!#REF!</xm:f>
+          </x14:formula1>
+          <xm:sqref>J1 L1:M1 C1:D1 G1:H1</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0200-000001000000}">
+          <x14:formula1>
+            <xm:f>'C:\Users\Area-Credit2\AppData\Local\Microsoft\Windows\INetCache\Content.Outlook\R4F19B9Y\[biblio  Globus (3).xls]rate code'!#REF!</xm:f>
+          </x14:formula1>
+          <xm:sqref>I1</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:N5"/>
-  <sheetFormatPr defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.28515625" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.5703125" style="2" customWidth="1"/>
-    <col min="3" max="13" width="12.7109375" style="2" customWidth="1"/>
-    <col min="14" max="16384" width="9.140625" style="2"/>
+    <col min="1" max="1" width="11.33203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.5546875" style="2" customWidth="1"/>
+    <col min="3" max="13" width="12.6640625" style="2" customWidth="1"/>
+    <col min="14" max="16384" width="9.109375" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="16.5" thickTop="1">
+    <row r="1" spans="1:14" ht="16.2" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A1" s="30" t="s">
         <v>5</v>
       </c>
@@ -4075,7 +4231,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:14" ht="14.25">
+    <row r="2" spans="1:14" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A2" s="32">
         <v>45668</v>
       </c>
@@ -4128,7 +4284,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="3" spans="1:14" ht="14.25">
+    <row r="3" spans="1:14" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A3" s="32">
         <v>45717</v>
       </c>
@@ -4181,7 +4337,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="4" spans="1:14" ht="14.25">
+    <row r="4" spans="1:14" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A4" s="32">
         <v>45764</v>
       </c>
@@ -4234,7 +4390,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="5" spans="1:14" ht="14.25">
+    <row r="5" spans="1:14" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A5" s="32">
         <v>45788</v>
       </c>
@@ -4288,32 +4444,42 @@
       </c>
     </row>
   </sheetData>
-  <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I1">
-      <formula1>'[2]rate code'!$A$1:$A$15</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J1 L1:M1 C1:D1 G1:H1">
-      <formula1>'[1]rate code'!$A$1:$A$15</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0300-000000000000}">
+          <x14:formula1>
+            <xm:f>'C:\Users\Area-Credit2\AppData\Local\Microsoft\Windows\INetCache\Content.Outlook\R4F19B9Y\[biblio  Globus (3).xls]rate code'!#REF!</xm:f>
+          </x14:formula1>
+          <xm:sqref>I1</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0300-000001000000}">
+          <x14:formula1>
+            <xm:f>'C:\Users\Area-Credit2\AppData\Local\Microsoft\Windows\INetCache\Content.Outlook\R4F19B9Y\[biblio Globus.xls]rate code'!#REF!</xm:f>
+          </x14:formula1>
+          <xm:sqref>J1 L1:M1 C1:D1 G1:H1</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:N11"/>
-  <sheetFormatPr defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.28515625" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.5703125" style="2" customWidth="1"/>
-    <col min="3" max="13" width="12.7109375" style="2" customWidth="1"/>
-    <col min="14" max="16384" width="9.140625" style="2"/>
+    <col min="1" max="1" width="11.33203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.5546875" style="2" customWidth="1"/>
+    <col min="3" max="13" width="12.6640625" style="2" customWidth="1"/>
+    <col min="14" max="16384" width="9.109375" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="16.5" thickTop="1">
+    <row r="1" spans="1:14" ht="16.2" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A1" s="30" t="s">
         <v>5</v>
       </c>
@@ -4357,7 +4523,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:14" ht="14.25">
+    <row r="2" spans="1:14" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A2" s="32">
         <v>45686</v>
       </c>
@@ -4410,7 +4576,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="3" spans="1:14" ht="14.25">
+    <row r="3" spans="1:14" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A3" s="32">
         <v>45717</v>
       </c>
@@ -4463,7 +4629,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="4" spans="1:14" ht="14.25">
+    <row r="4" spans="1:14" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A4" s="32">
         <v>45764</v>
       </c>
@@ -4516,7 +4682,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="5" spans="1:14" ht="14.25">
+    <row r="5" spans="1:14" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A5" s="32">
         <v>45788</v>
       </c>
@@ -4569,7 +4735,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="6" spans="1:14" ht="14.25">
+    <row r="6" spans="1:14" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A6" s="32">
         <v>45793</v>
       </c>
@@ -4622,7 +4788,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="7" spans="1:14" ht="14.25">
+    <row r="7" spans="1:14" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A7" s="32">
         <v>45809</v>
       </c>
@@ -4675,7 +4841,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="8" spans="1:14" ht="14.25">
+    <row r="8" spans="1:14" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A8" s="32">
         <v>45839</v>
       </c>
@@ -4728,7 +4894,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="9" spans="1:14" ht="14.25">
+    <row r="9" spans="1:14" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A9" s="32">
         <v>45870</v>
       </c>
@@ -4781,7 +4947,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="10" spans="1:14" ht="14.25">
+    <row r="10" spans="1:14" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A10" s="32">
         <v>45901</v>
       </c>
@@ -4834,7 +5000,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="11" spans="1:14" ht="14.25">
+    <row r="11" spans="1:14" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A11" s="32">
         <v>45931</v>
       </c>
@@ -4888,32 +5054,42 @@
       </c>
     </row>
   </sheetData>
-  <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J1 L1:M1 C1:D1 G1:H1">
-      <formula1>'[1]rate code'!$A$1:$A$15</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I1">
-      <formula1>'[2]rate code'!$A$1:$A$15</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0400-000000000000}">
+          <x14:formula1>
+            <xm:f>'C:\Users\Area-Credit2\AppData\Local\Microsoft\Windows\INetCache\Content.Outlook\R4F19B9Y\[biblio Globus.xls]rate code'!#REF!</xm:f>
+          </x14:formula1>
+          <xm:sqref>J1 L1:M1 C1:D1 G1:H1</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0400-000001000000}">
+          <x14:formula1>
+            <xm:f>'C:\Users\Area-Credit2\AppData\Local\Microsoft\Windows\INetCache\Content.Outlook\R4F19B9Y\[biblio  Globus (3).xls]rate code'!#REF!</xm:f>
+          </x14:formula1>
+          <xm:sqref>I1</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:N10"/>
-  <sheetFormatPr defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.28515625" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.5703125" style="2" customWidth="1"/>
-    <col min="3" max="13" width="12.7109375" style="2" customWidth="1"/>
-    <col min="14" max="16384" width="9.140625" style="2"/>
+    <col min="1" max="1" width="11.33203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.5546875" style="2" customWidth="1"/>
+    <col min="3" max="13" width="12.6640625" style="2" customWidth="1"/>
+    <col min="14" max="16384" width="9.109375" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="16.5" thickTop="1">
+    <row r="1" spans="1:14" ht="16.2" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A1" s="30" t="s">
         <v>5</v>
       </c>
@@ -4957,7 +5133,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:14" ht="14.25">
+    <row r="2" spans="1:14" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A2" s="32">
         <v>45732</v>
       </c>
@@ -5010,7 +5186,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="3" spans="1:14" ht="14.25">
+    <row r="3" spans="1:14" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A3" s="32">
         <v>45764</v>
       </c>
@@ -5063,7 +5239,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="4" spans="1:14" ht="14.25">
+    <row r="4" spans="1:14" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A4" s="32">
         <v>45788</v>
       </c>
@@ -5116,7 +5292,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="5" spans="1:14" ht="14.25">
+    <row r="5" spans="1:14" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A5" s="32">
         <v>45793</v>
       </c>
@@ -5169,7 +5345,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="6" spans="1:14" ht="14.25">
+    <row r="6" spans="1:14" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A6" s="32">
         <v>45809</v>
       </c>
@@ -5222,7 +5398,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="7" spans="1:14" ht="14.25">
+    <row r="7" spans="1:14" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A7" s="32">
         <v>45839</v>
       </c>
@@ -5275,7 +5451,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="8" spans="1:14" ht="14.25">
+    <row r="8" spans="1:14" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A8" s="32">
         <v>45870</v>
       </c>
@@ -5328,7 +5504,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="9" spans="1:14" ht="14.25">
+    <row r="9" spans="1:14" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A9" s="32">
         <v>45901</v>
       </c>
@@ -5381,7 +5557,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="10" spans="1:14" ht="14.25">
+    <row r="10" spans="1:14" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A10" s="32">
         <v>45931</v>
       </c>
@@ -5435,16 +5611,26 @@
       </c>
     </row>
   </sheetData>
-  <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J1 L1:M1 C1:D1 G1:H1">
-      <formula1>'[1]rate code'!$A$1:$A$15</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I1">
-      <formula1>'[2]rate code'!$A$1:$A$15</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0500-000000000000}">
+          <x14:formula1>
+            <xm:f>'C:\Users\Area-Credit2\AppData\Local\Microsoft\Windows\INetCache\Content.Outlook\R4F19B9Y\[biblio Globus.xls]rate code'!#REF!</xm:f>
+          </x14:formula1>
+          <xm:sqref>J1 L1:M1 C1:D1 G1:H1</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0500-000001000000}">
+          <x14:formula1>
+            <xm:f>'C:\Users\Area-Credit2\AppData\Local\Microsoft\Windows\INetCache\Content.Outlook\R4F19B9Y\[biblio  Globus (3).xls]rate code'!#REF!</xm:f>
+          </x14:formula1>
+          <xm:sqref>I1</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
 </worksheet>
 </file>